--- a/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuMayTinhTien.xlsx
@@ -727,32 +727,32 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTT</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>077196000132</t>
+          <t>077082002684</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
+          <t>HỘ KINH DOANH CỬA HÀNG HOÀI MINH ANH</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 41Y, khu phố Long Phượng, Xã Long Điền, TP Hồ Chí Minh</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -772,7 +772,7 @@
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>3565000.0</v>
+        <v>4440000.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -791,37 +791,37 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C26MRV</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1573</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3500704465</t>
+          <t>077196000132</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH RỒNG VIỆT</t>
+          <t>Nguyễn Thị Minh Tuyền (Nhà Cung cấp hiền trang)</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+          <t>441/6/4 đường Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -835,17 +835,13 @@
         </is>
       </c>
       <c r="K14" s="6"/>
-      <c r="L14" s="13" t="n">
-        <v>1218720.0</v>
-      </c>
-      <c r="M14" s="13" t="n">
-        <v>97498.0</v>
-      </c>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
       <c r="N14" s="13" t="n">
-        <v>154080.0</v>
+        <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1316218.0</v>
+        <v>3565000.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -874,12 +870,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>1573</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -909,16 +905,16 @@
       </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>4656756.0</v>
+        <v>1218720.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>372540.0</v>
+        <v>97498.0</v>
       </c>
       <c r="N15" s="13" t="n">
-        <v>340244.0</v>
+        <v>154080.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>5029296.0</v>
+        <v>1316218.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -947,12 +943,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>176</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -982,16 +978,16 @@
       </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>3577148.0</v>
+        <v>4656756.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>286172.0</v>
+        <v>372540.0</v>
       </c>
       <c r="N16" s="13" t="n">
-        <v>52972.0</v>
+        <v>340244.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>3863320.0</v>
+        <v>5029296.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1020,7 +1016,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -1055,16 +1051,16 @@
       </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>487872.0</v>
+        <v>3577148.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>39030.0</v>
+        <v>286172.0</v>
       </c>
       <c r="N17" s="13" t="n">
-        <v>66528.0</v>
+        <v>52972.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>526902.0</v>
+        <v>3863320.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1093,12 +1089,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1128,16 +1124,16 @@
       </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>1395384.0</v>
+        <v>487872.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>111631.0</v>
+        <v>39030.0</v>
       </c>
       <c r="N18" s="13" t="n">
-        <v>5016.0</v>
+        <v>66528.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1507015.0</v>
+        <v>526902.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1166,7 +1162,7 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -1201,16 +1197,16 @@
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>1981836.0</v>
+        <v>1395384.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>158547.0</v>
+        <v>111631.0</v>
       </c>
       <c r="N19" s="13" t="n">
-        <v>8964.0</v>
+        <v>5016.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>2140383.0</v>
+        <v>1507015.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1239,12 +1235,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1274,16 +1270,16 @@
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>2895339.0</v>
+        <v>1981836.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>231627.0</v>
+        <v>158547.0</v>
       </c>
       <c r="N20" s="13" t="n">
-        <v>232161.0</v>
+        <v>8964.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>3126966.0</v>
+        <v>2140383.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1312,12 +1308,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>16/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1347,16 +1343,16 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>3723144.0</v>
+        <v>2895339.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>297852.0</v>
+        <v>231627.0</v>
       </c>
       <c r="N21" s="13" t="n">
-        <v>50456.0</v>
+        <v>232161.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>4020996.0</v>
+        <v>3126966.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1385,12 +1381,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>17/01/2026</t>
+          <t>16/01/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1415,21 +1411,21 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>1814815.0</v>
+        <v>3723144.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>145185.0</v>
+        <v>297852.0</v>
       </c>
       <c r="N22" s="13" t="n">
-        <v>306185.0</v>
+        <v>50456.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>1960000.0</v>
+        <v>4020996.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1458,12 +1454,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>17/01/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1493,16 +1489,16 @@
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>1.6574074E7</v>
+        <v>1814815.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>1325926.0</v>
+        <v>145185.0</v>
       </c>
       <c r="N23" s="13" t="n">
-        <v>801926.0</v>
+        <v>306185.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>1.79E7</v>
+        <v>1960000.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1531,12 +1527,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1561,21 +1557,21 @@
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>1478472.0</v>
+        <v>1.6574074E7</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>118278.0</v>
+        <v>1325926.0</v>
       </c>
       <c r="N24" s="13" t="n">
-        <v>28488.0</v>
+        <v>801926.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>1596750.0</v>
+        <v>1.79E7</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1604,12 +1600,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1639,16 +1635,16 @@
       </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>4377168.0</v>
+        <v>1478472.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>350173.0</v>
+        <v>118278.0</v>
       </c>
       <c r="N25" s="13" t="n">
-        <v>10032.0</v>
+        <v>28488.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>4727341.0</v>
+        <v>1596750.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1677,7 +1673,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>388</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -1712,16 +1708,16 @@
       </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>3237984.0</v>
+        <v>4377168.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>259039.0</v>
+        <v>350173.0</v>
       </c>
       <c r="N26" s="13" t="n">
-        <v>210816.0</v>
+        <v>10032.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>3497023.0</v>
+        <v>4727341.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1750,12 +1746,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>389</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>22/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1785,16 +1781,16 @@
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>1058899.0</v>
+        <v>3237984.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>84712.0</v>
+        <v>259039.0</v>
       </c>
       <c r="N27" s="13" t="n">
-        <v>198701.0</v>
+        <v>210816.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>1143611.0</v>
+        <v>3497023.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1823,12 +1819,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>22/01/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1858,16 +1854,16 @@
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>3159773.0</v>
+        <v>1058899.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>252782.0</v>
+        <v>84712.0</v>
       </c>
       <c r="N28" s="13" t="n">
-        <v>94587.0</v>
+        <v>198701.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>3412555.0</v>
+        <v>1143611.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1896,12 +1892,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>24/01/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1931,16 +1927,16 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>0.0</v>
+        <v>3159773.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>0.0</v>
+        <v>252782.0</v>
       </c>
       <c r="N29" s="13" t="n">
-        <v>0.0</v>
+        <v>94587.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>0.0</v>
+        <v>3412555.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1969,7 +1965,7 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -2004,16 +2000,16 @@
       </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>1106305.0</v>
+        <v>0.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>88504.0</v>
+        <v>0.0</v>
       </c>
       <c r="N30" s="13" t="n">
-        <v>16995.0</v>
+        <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>1194809.0</v>
+        <v>0.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -2042,12 +2038,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>24/01/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2077,16 +2073,16 @@
       </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>2116879.0</v>
+        <v>1106305.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>169350.0</v>
+        <v>88504.0</v>
       </c>
       <c r="N31" s="13" t="n">
-        <v>19821.0</v>
+        <v>16995.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>2286229.0</v>
+        <v>1194809.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2115,12 +2111,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2145,21 +2141,21 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>1904756.0</v>
+        <v>3.4027778E7</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>152380.0</v>
+        <v>2722222.0</v>
       </c>
       <c r="N32" s="13" t="n">
-        <v>11044.0</v>
+        <v>2032222.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>2057136.0</v>
+        <v>3.675E7</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2183,32 +2179,32 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C26MBM</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -2223,16 +2219,16 @@
       </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>5.4409091E7</v>
+        <v>2466150.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>5440909.0</v>
+        <v>197292.0</v>
       </c>
       <c r="N33" s="13" t="n">
-        <v>0.0</v>
+        <v>56450.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>5.985E7</v>
+        <v>2663442.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2256,32 +2252,32 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -2296,16 +2292,16 @@
       </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>8064814.0</v>
+        <v>1075511.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>645186.0</v>
+        <v>86041.0</v>
       </c>
       <c r="N34" s="13" t="n">
-        <v>0.0</v>
+        <v>143889.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>8710000.0</v>
+        <v>1161552.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2329,32 +2325,32 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C26MRT</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>859</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3501013206</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -2369,16 +2365,16 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>2.8829629E7</v>
+        <v>2116879.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>2306371.0</v>
+        <v>169350.0</v>
       </c>
       <c r="N35" s="13" t="n">
-        <v>0.0</v>
+        <v>19821.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>3.1136E7</v>
+        <v>2286229.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2402,32 +2398,32 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C26MTK</t>
+          <t>C26MRV</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>860</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502242819</t>
+          <t>3500704465</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THOẠI KHANG</t>
+          <t>CÔNG TY TNHH RỒNG VIỆT</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>Số 863 Đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -2442,14 +2438,16 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>1.164E7</v>
+        <v>1904756.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1164000.0</v>
-      </c>
-      <c r="N36" s="13"/>
+        <v>152380.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>11044.0</v>
+      </c>
       <c r="O36" s="13" t="n">
-        <v>1.2804E7</v>
+        <v>2057136.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2473,32 +2471,32 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C26MHT</t>
+          <t>C26MBM</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>654</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>23/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502324074</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -2513,16 +2511,16 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>4.89804E8</v>
+        <v>5.4409091E7</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>4.89804E7</v>
+        <v>5440909.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>5.387844E8</v>
+        <v>5.985E7</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2546,32 +2544,32 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -2586,16 +2584,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>3916330.0</v>
+        <v>8064814.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>373670.0</v>
+        <v>645186.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>4290000.0</v>
+        <v>8710000.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2619,32 +2617,32 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MRT</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3501013206</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI BẠCH MAI</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 01A Tô Nguyệt Đình, Phường Long Hương, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -2659,16 +2657,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>2.720909E7</v>
+        <v>2.8829629E7</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>2720910.0</v>
+        <v>2306371.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>2.993E7</v>
+        <v>3.1136E7</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2692,32 +2690,32 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MTK</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>393</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>15/01/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502242819</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THOẠI KHANG</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>36 Trường Chinh, Khu phố Hải An, Xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -2732,16 +2730,14 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>6472727.0</v>
+        <v>1.164E7</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>647273.0</v>
-      </c>
-      <c r="N40" s="13" t="n">
-        <v>0.0</v>
-      </c>
+        <v>1164000.0</v>
+      </c>
+      <c r="N40" s="13"/>
       <c r="O40" s="13" t="n">
-        <v>7120000.0</v>
+        <v>1.2804E7</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2765,32 +2761,32 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C26MTD</t>
+          <t>C26MHT</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>224</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>23/01/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502344144</t>
+          <t>3502324074</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ HƯƠNG THỊNH PHÁT</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>69 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -2805,16 +2801,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>3.9173905E7</v>
+        <v>4.89804E8</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>3276095.0</v>
+        <v>4.89804E7</v>
       </c>
       <c r="N41" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>4.245E7</v>
+        <v>5.387844E8</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2843,12 +2839,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2878,16 +2874,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>3.9664546E7</v>
+        <v>3916330.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>3966455.0</v>
+        <v>373670.0</v>
       </c>
       <c r="N42" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>4.3631001E7</v>
+        <v>4290000.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2911,32 +2907,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2951,16 +2947,16 @@
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>3089351.0</v>
+        <v>2.720909E7</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>247149.0</v>
+        <v>2720910.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>3336500.0</v>
+        <v>2.993E7</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2984,32 +2980,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C26MDH</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>15/01/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3024,16 +3020,16 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>1367592.0</v>
+        <v>6472727.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>109408.0</v>
+        <v>647273.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>1477000.0</v>
+        <v>7120000.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -3057,32 +3053,32 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C26MNB</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>248</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>13/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3502437617</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -3097,16 +3093,16 @@
       </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>5.9970002E7</v>
+        <v>3.9173905E7</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>5540718.0</v>
+        <v>3276095.0</v>
       </c>
       <c r="N45" s="13" t="n">
-        <v>1214983.0</v>
+        <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>6.551072E7</v>
+        <v>4.245E7</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -3130,32 +3126,32 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MTD</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>20/01/2026</t>
+          <t>10/01/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3165,21 +3161,21 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>1.8727272E7</v>
+        <v>3.9664546E7</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1872727.0</v>
+        <v>3966455.0</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>2.0599999E7</v>
+        <v>4.3631001E7</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3203,32 +3199,32 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
@@ -3238,21 +3234,21 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>3.1825652E7</v>
+        <v>3089351.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>3182565.0</v>
+        <v>247149.0</v>
       </c>
       <c r="N47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>3.5008217E7</v>
+        <v>3336500.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3276,32 +3272,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C26MYY</t>
+          <t>C26MDH</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3311,21 +3307,21 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>2.6727272E7</v>
+        <v>1367592.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>2672727.0</v>
+        <v>109408.0</v>
       </c>
       <c r="N48" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>2.9399999E7</v>
+        <v>1477000.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3349,32 +3345,32 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MNB</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>177</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>13/01/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502437617</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH NƯỚC GIẢI KHÁT NHUNG BÌNH</t>
         </is>
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>152, tổ 5, Khu Phố 2, Phường Tam Long, Thành phố Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -3389,16 +3385,16 @@
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>1398148.0</v>
+        <v>5.9970002E7</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>111852.0</v>
+        <v>5540718.0</v>
       </c>
       <c r="N49" s="13" t="n">
-        <v>0.0</v>
+        <v>1214983.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>1510000.0</v>
+        <v>6.551072E7</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3422,32 +3418,32 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C26MNL</t>
+          <t>C26MYY</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>234</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>20/01/2026</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3502547930</t>
+          <t>3502483525</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
         </is>
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -3457,28 +3453,320 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
         </is>
       </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>2.157776E7</v>
+        <v>1.8727272E7</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>1726221.0</v>
+        <v>1872727.0</v>
       </c>
       <c r="N50" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
+        <v>2.0599999E7</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>3.1825652E7</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>3182565.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>3.5008217E7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C26MYY</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>2.6727272E7</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>2672727.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>2.9399999E7</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>05/01/2026</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>1398148.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>111852.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>1510000.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C26MNL</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502547930</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH  PHÁT TRIỂN THƯƠNG MẠI TÂM NGUYÊN LONG</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>199 Đường 2/9, Phường Tam Thắng, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>2.157776E7</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>1726221.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
         <v>2.3303981E7</v>
       </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
